--- a/職務経歴書.xlsx
+++ b/職務経歴書.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nishimura Shuichi\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nishimura Shuichi\Desktop\Employment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21F5301F-BA9C-41AF-AD4E-24A3AE0FE023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F996ECB-DA93-4617-ADB8-90EFE96E01DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5E62391C-9EF7-4F4E-82A9-F69ECBB21400}"/>
   </bookViews>
@@ -28,12 +28,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
   <si>
     <t>【職務要約】</t>
-  </si>
-  <si>
-    <t>例：大学卒業後、〇〇会社において〇〇に従事してまいりました。〇〇を経験しております。〇〇として現在に至ります。</t>
   </si>
   <si>
     <t>【職務経歴】</t>
@@ -102,6 +99,114 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>シュウイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：専門学校でゲームに関しての基本的なプログラムなどを学び、現在に至ります</t>
+    <rPh sb="2" eb="6">
+      <t>センモンガッコウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>マナ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>イタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>会社名・部署：JA全農ミートフーズ　</t>
+    <rPh sb="0" eb="3">
+      <t>カイシャメイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ブショ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ゼンノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>業務内容等　主に肉を産地ごとにに仕分け、それを乗せる台などの清掃もしたりしました。そこでレーンなどの共同作業をする中で、相手に対してのサポートや現場の状況把握力などを活かし、仕事の効率を40%上げる事に成功しました。</t>
+    <rPh sb="0" eb="2">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナド</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ニク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サンチ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シワ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>セイソウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>キョウドウ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>ゲンバ</t>
+    </rPh>
+    <rPh sb="77" eb="80">
+      <t>ハアクリョク</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>コウリツ</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>セイコウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -414,6 +519,57 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="55" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -432,6 +588,15 @@
     <xf numFmtId="55" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -441,15 +606,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -494,57 +650,6 @@
     </xf>
     <xf numFmtId="55" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -872,34 +977,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.4">
-      <c r="A1" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
+      <c r="A1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
+      <c r="A2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
     </row>
     <row r="3" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="2"/>
@@ -908,20 +1013,20 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
+        <v>5</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
     </row>
     <row r="4" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
       <c r="D4" s="2"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -932,78 +1037,78 @@
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="13"/>
+    </row>
+    <row r="7" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="13"/>
+    </row>
+    <row r="8" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="14"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="16"/>
+    </row>
+    <row r="9" spans="1:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+    </row>
+    <row r="10" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="40"/>
-    </row>
-    <row r="6" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="41"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="43"/>
-    </row>
-    <row r="7" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="41"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="43"/>
-    </row>
-    <row r="8" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="44"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="46"/>
-    </row>
-    <row r="9" spans="1:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="48"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-    </row>
-    <row r="10" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="47" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -1014,442 +1119,433 @@
       <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="22"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="34" t="s">
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="23"/>
+    </row>
+    <row r="12" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="45">
+        <v>45383</v>
+      </c>
+      <c r="B12" s="46"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="35"/>
+    </row>
+    <row r="13" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="38"/>
+    </row>
+    <row r="14" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="41"/>
+    </row>
+    <row r="15" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="36"/>
-    </row>
-    <row r="12" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="28">
-        <v>40269</v>
-      </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="13" t="s">
+      <c r="B15" s="31"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="41"/>
+    </row>
+    <row r="16" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="24">
+        <v>45911</v>
+      </c>
+      <c r="B16" s="25"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="41"/>
+    </row>
+    <row r="17" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="41"/>
+    </row>
+    <row r="18" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="27"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="44"/>
+    </row>
+    <row r="19" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="46"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="35"/>
+    </row>
+    <row r="20" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="48"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="15"/>
-    </row>
-    <row r="13" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="31"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="19" t="s">
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="38"/>
+    </row>
+    <row r="21" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="48"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="41"/>
+    </row>
+    <row r="22" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="31"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="41"/>
+    </row>
+    <row r="23" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="21"/>
-    </row>
-    <row r="14" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="31"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="24"/>
-    </row>
-    <row r="15" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="24"/>
-    </row>
-    <row r="16" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="7">
-        <v>44105</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="24"/>
-    </row>
-    <row r="17" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="7"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="24"/>
-    </row>
-    <row r="18" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="27"/>
-    </row>
-    <row r="19" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="13" t="s">
+      <c r="B23" s="25"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="41"/>
+    </row>
+    <row r="24" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="41"/>
+    </row>
+    <row r="25" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="27"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="44"/>
+    </row>
+    <row r="26" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="35"/>
+    </row>
+    <row r="27" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="48"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="15"/>
-    </row>
-    <row r="20" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="31"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="19" t="s">
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="38"/>
+    </row>
+    <row r="28" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="48"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="41"/>
+    </row>
+    <row r="29" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="31"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="41"/>
+    </row>
+    <row r="30" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="21"/>
-    </row>
-    <row r="21" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="31"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="24"/>
-    </row>
-    <row r="22" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="24"/>
-    </row>
-    <row r="23" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="24"/>
-    </row>
-    <row r="24" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="7"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="24"/>
-    </row>
-    <row r="25" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="10"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="27"/>
-    </row>
-    <row r="26" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="13" t="s">
+      <c r="B30" s="25"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="40"/>
+      <c r="K30" s="41"/>
+    </row>
+    <row r="31" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="24"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="41"/>
+    </row>
+    <row r="32" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="27"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="44"/>
+    </row>
+    <row r="33" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="46"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="35"/>
+    </row>
+    <row r="34" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="48"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="15"/>
-    </row>
-    <row r="27" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="31"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="19" t="s">
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="38"/>
+    </row>
+    <row r="35" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="48"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="41"/>
+    </row>
+    <row r="36" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="31"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="40"/>
+      <c r="J36" s="40"/>
+      <c r="K36" s="41"/>
+    </row>
+    <row r="37" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="21"/>
-    </row>
-    <row r="28" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="31"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="24"/>
-    </row>
-    <row r="29" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="24"/>
-    </row>
-    <row r="30" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="24"/>
-    </row>
-    <row r="31" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="7"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="23"/>
-      <c r="K31" s="24"/>
-    </row>
-    <row r="32" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="10"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="27"/>
-    </row>
-    <row r="33" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" s="29"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="15"/>
-    </row>
-    <row r="34" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="31"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="21"/>
-    </row>
-    <row r="35" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="31"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="33"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="23"/>
-      <c r="K35" s="24"/>
-    </row>
-    <row r="36" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="23"/>
-      <c r="K36" s="24"/>
-    </row>
-    <row r="37" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
-      <c r="J37" s="23"/>
-      <c r="K37" s="24"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="40"/>
+      <c r="K37" s="41"/>
     </row>
     <row r="38" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="7"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="23"/>
-      <c r="K38" s="24"/>
+      <c r="A38" s="24"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="40"/>
+      <c r="K38" s="41"/>
     </row>
     <row r="39" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="10"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="27"/>
+      <c r="A39" s="27"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A5:K8"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="D11:K11"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A16:C18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D12:K12"/>
-    <mergeCell ref="D13:K18"/>
-    <mergeCell ref="A12:C14"/>
+    <mergeCell ref="A37:C39"/>
+    <mergeCell ref="D33:K33"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="D34:K39"/>
+    <mergeCell ref="A33:C35"/>
     <mergeCell ref="A30:C32"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C25"/>
@@ -1460,11 +1556,20 @@
     <mergeCell ref="A19:C21"/>
     <mergeCell ref="A26:C28"/>
     <mergeCell ref="D19:K19"/>
-    <mergeCell ref="A37:C39"/>
-    <mergeCell ref="D33:K33"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="D34:K39"/>
-    <mergeCell ref="A33:C35"/>
+    <mergeCell ref="D11:K11"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A16:C18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D12:K12"/>
+    <mergeCell ref="D13:K18"/>
+    <mergeCell ref="A12:C14"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A5:K8"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I3:K3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>

--- a/職務経歴書.xlsx
+++ b/職務経歴書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nishimura Shuichi\Desktop\Employment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F996ECB-DA93-4617-ADB8-90EFE96E01DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC0C632-3378-495E-9856-F8E3C3610662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5E62391C-9EF7-4F4E-82A9-F69ECBB21400}"/>
   </bookViews>
@@ -20,6 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -28,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>【職務要約】</t>
   </si>
@@ -56,43 +65,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>会社名・部署：</t>
-    <rPh sb="0" eb="3">
-      <t>カイシャメイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ブショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>業務内容等</t>
-    <rPh sb="0" eb="2">
-      <t>ギョウム</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ナド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　年　 月</t>
-    <rPh sb="1" eb="2">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ツキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2025年9月11日現在</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>西村　柊一</t>
     <rPh sb="0" eb="2">
       <t>ニシムラ</t>
@@ -138,7 +110,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>業務内容等　主に肉を産地ごとにに仕分け、それを乗せる台などの清掃もしたりしました。そこでレーンなどの共同作業をする中で、相手に対してのサポートや現場の状況把握力などを活かし、仕事の効率を40%上げる事に成功しました。</t>
+    <t>業務内容等　主に肉を産地ごとにに仕分け、それを乗せる台などの清掃もしたりしました。そこでレーンなどの共同作業をする中で、相手に対してのサポートや現場の状況把握力などを活かし、仕事の効率を30%上げる事に成功しました。</t>
     <rPh sb="0" eb="2">
       <t>ギョウム</t>
     </rPh>
@@ -497,7 +469,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -518,6 +490,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -968,7 +943,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultColWidth="7" defaultRowHeight="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="3" width="6.25" style="1" customWidth="1"/>
@@ -977,34 +952,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
     </row>
     <row r="2" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
+      <c r="A2" s="20" t="str">
+        <f ca="1">TEXT(TODAY(),"yyyy年m月d日現在")</f>
+        <v>2025年9月25日現在</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
     </row>
     <row r="3" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="2"/>
@@ -1015,18 +991,18 @@
       <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
+      <c r="I3" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
       <c r="D4" s="2"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -1037,78 +1013,78 @@
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="10"/>
+      <c r="A5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="11"/>
     </row>
     <row r="6" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="13"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="14"/>
     </row>
     <row r="7" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="13"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="16"/>
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="17"/>
     </row>
     <row r="9" spans="1:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
     </row>
     <row r="10" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -1119,443 +1095,129 @@
       <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="21" t="s">
+      <c r="B11" s="23"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="24"/>
     </row>
     <row r="12" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="45">
+      <c r="A12" s="46">
         <v>45383</v>
       </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="35"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="36"/>
     </row>
     <row r="13" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="48"/>
-      <c r="B13" s="49"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="38"/>
+      <c r="A13" s="49"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="39"/>
     </row>
     <row r="14" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="48"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="41"/>
+      <c r="A14" s="49"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="42"/>
     </row>
     <row r="15" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="41"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="42"/>
     </row>
     <row r="16" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="24">
-        <v>45911</v>
-      </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="41"/>
+      <c r="A16" s="25">
+        <f ca="1">TODAY()</f>
+        <v>45925</v>
+      </c>
+      <c r="B16" s="26"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="42"/>
     </row>
     <row r="17" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="41"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="42"/>
     </row>
     <row r="18" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="27"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="44"/>
-    </row>
-    <row r="19" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="46"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="35"/>
-    </row>
-    <row r="20" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="48"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="38"/>
-    </row>
-    <row r="21" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="48"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="41"/>
-    </row>
-    <row r="22" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="41"/>
-    </row>
-    <row r="23" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="41"/>
-    </row>
-    <row r="24" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="41"/>
-    </row>
-    <row r="25" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="27"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="44"/>
-    </row>
-    <row r="26" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="46"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="35"/>
-    </row>
-    <row r="27" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="48"/>
-      <c r="B27" s="49"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="38"/>
-    </row>
-    <row r="28" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="48"/>
-      <c r="B28" s="49"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="41"/>
-    </row>
-    <row r="29" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="40"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="41"/>
-    </row>
-    <row r="30" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="25"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
-      <c r="K30" s="41"/>
-    </row>
-    <row r="31" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="24"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="40"/>
-      <c r="K31" s="41"/>
-    </row>
-    <row r="32" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="27"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="43"/>
-      <c r="J32" s="43"/>
-      <c r="K32" s="44"/>
-    </row>
-    <row r="33" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="B33" s="46"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="35"/>
-    </row>
-    <row r="34" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="48"/>
-      <c r="B34" s="49"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="38"/>
-    </row>
-    <row r="35" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="48"/>
-      <c r="B35" s="49"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="40"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="40"/>
-      <c r="K35" s="41"/>
-    </row>
-    <row r="36" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="31"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="40"/>
-      <c r="K36" s="41"/>
-    </row>
-    <row r="37" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="25"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="40"/>
-      <c r="K37" s="41"/>
-    </row>
-    <row r="38" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="24"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="40"/>
-      <c r="K38" s="41"/>
-    </row>
-    <row r="39" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="27"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="43"/>
-      <c r="H39" s="43"/>
-      <c r="I39" s="43"/>
-      <c r="J39" s="43"/>
-      <c r="K39" s="44"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="45"/>
+    </row>
+    <row r="41" spans="4:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="D41" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="A37:C39"/>
-    <mergeCell ref="D33:K33"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="D34:K39"/>
-    <mergeCell ref="A33:C35"/>
-    <mergeCell ref="A30:C32"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C25"/>
-    <mergeCell ref="D26:K26"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="D20:K25"/>
-    <mergeCell ref="D27:K32"/>
-    <mergeCell ref="A19:C21"/>
-    <mergeCell ref="A26:C28"/>
-    <mergeCell ref="D19:K19"/>
+  <mergeCells count="14">
     <mergeCell ref="D11:K11"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A16:C18"/>

--- a/職務経歴書.xlsx
+++ b/職務経歴書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nishimura Shuichi\Desktop\Employment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC0C632-3378-495E-9856-F8E3C3610662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5F3306-DA80-4189-ADD9-0C761E574A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5E62391C-9EF7-4F4E-82A9-F69ECBB21400}"/>
   </bookViews>
@@ -110,75 +110,12 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>業務内容等　主に肉を産地ごとにに仕分け、それを乗せる台などの清掃もしたりしました。そこでレーンなどの共同作業をする中で、相手に対してのサポートや現場の状況把握力などを活かし、仕事の効率を30%上げる事に成功しました。</t>
+    <t>事業内容：主に食肉を産地ごとに仕分ける作業に従事し、併せて作業台などの清掃業務も担当いたしました。コンベアラインでの共同作業においては、作業者間の連携を重視し、相手へのサポートや現場の状況把握に努めました。その結果、作業効率を約30%向上させることに成功し、常に迅速かつ正確な作業完了を目指して行動いたしました。</t>
     <rPh sb="0" eb="2">
-      <t>ギョウム</t>
+      <t>ジギョウ</t>
     </rPh>
     <rPh sb="2" eb="4">
       <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ナド</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>オモ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ニク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>サンチ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>シワ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ノ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>セイソウ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>キョウドウ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>サギョウ</t>
-    </rPh>
-    <rPh sb="57" eb="58">
-      <t>ナカ</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="63" eb="64">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="72" eb="74">
-      <t>ゲンバ</t>
-    </rPh>
-    <rPh sb="77" eb="80">
-      <t>ハアクリョク</t>
-    </rPh>
-    <rPh sb="83" eb="84">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="87" eb="89">
-      <t>シゴト</t>
-    </rPh>
-    <rPh sb="90" eb="92">
-      <t>コウリツ</t>
-    </rPh>
-    <rPh sb="96" eb="97">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="99" eb="100">
-      <t>コト</t>
-    </rPh>
-    <rPh sb="101" eb="103">
-      <t>セイコウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -967,9 +904,9 @@
       <c r="K1" s="8"/>
     </row>
     <row r="2" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="20" t="str">
-        <f ca="1">TEXT(TODAY(),"yyyy年m月d日現在")</f>
-        <v>2025年9月25日現在</v>
+      <c r="A2" s="20">
+        <f>P3</f>
+        <v>0</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -1174,7 +1111,7 @@
     <row r="16" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="25">
         <f ca="1">TODAY()</f>
-        <v>45925</v>
+        <v>45936</v>
       </c>
       <c r="B16" s="26"/>
       <c r="C16" s="27"/>

--- a/職務経歴書.xlsx
+++ b/職務経歴書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nishimura Shuichi\Desktop\Employment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5F3306-DA80-4189-ADD9-0C761E574A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F969EF69-D984-420F-8563-E7C54EAC5683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5E62391C-9EF7-4F4E-82A9-F69ECBB21400}"/>
   </bookViews>
@@ -75,28 +75,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>例：専門学校でゲームに関しての基本的なプログラムなどを学び、現在に至ります</t>
-    <rPh sb="2" eb="6">
-      <t>センモンガッコウ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>キホンテキ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>マナ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>イタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>会社名・部署：JA全農ミートフーズ　</t>
     <rPh sb="0" eb="3">
       <t>カイシャメイ</t>
@@ -116,6 +94,16 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：物流倉庫にて約1年半、ピッキング作業に従事。1日平均200件以上の仕分出荷業務を正確かつ迅速に処理し、誤出荷率0.1%以下を維持しました。作業効率と正確性を両立させる重要性を学び、細部への注意力と集中力を養いました</t>
+    <rPh sb="11" eb="12">
+      <t>ハン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>シワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -431,6 +419,96 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="55" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="55" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="55" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="55" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="55" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="55" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="55" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="55" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="55" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="55" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="55" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="55" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -472,96 +550,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="55" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="55" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="55" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="55" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="55" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="55" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="55" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="55" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="55" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="55" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="55" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="55" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -889,35 +877,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
     </row>
     <row r="2" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="20">
-        <f>P3</f>
-        <v>0</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
+      <c r="A2" s="50" t="str">
+        <f ca="1">TEXT(TODAY(),"m月d日") &amp; "現在"</f>
+        <v>10月10日現在</v>
+      </c>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
     </row>
     <row r="3" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="2"/>
@@ -928,18 +916,18 @@
       <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
     </row>
     <row r="4" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
       <c r="D4" s="2"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -950,78 +938,78 @@
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="11"/>
+      <c r="A5" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="41"/>
     </row>
     <row r="6" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="14"/>
+      <c r="A6" s="42"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="44"/>
     </row>
     <row r="7" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="14"/>
+      <c r="A7" s="42"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="44"/>
     </row>
     <row r="8" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="17"/>
+      <c r="A8" s="45"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="47"/>
     </row>
     <row r="9" spans="1:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="49"/>
     </row>
     <row r="10" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -1032,129 +1020,136 @@
       <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="22" t="s">
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="24"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="46">
+      <c r="A12" s="32">
         <v>45383</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="34" t="s">
+      <c r="B12" s="33"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="22"/>
+    </row>
+    <row r="13" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="35"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="36"/>
-    </row>
-    <row r="13" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="49"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="39"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="25"/>
     </row>
     <row r="14" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="49"/>
-      <c r="B14" s="50"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="42"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="28"/>
     </row>
     <row r="15" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="42"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="28"/>
     </row>
     <row r="16" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25">
+      <c r="A16" s="11">
         <f ca="1">TODAY()</f>
-        <v>45936</v>
-      </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="42"/>
+        <v>45940</v>
+      </c>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="28"/>
     </row>
     <row r="17" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="42"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="28"/>
     </row>
     <row r="18" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
-      <c r="K18" s="45"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="31"/>
     </row>
     <row r="41" spans="4:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D41" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A5:K8"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I3:K3"/>
     <mergeCell ref="D11:K11"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A16:C18"/>
@@ -1162,13 +1157,6 @@
     <mergeCell ref="D12:K12"/>
     <mergeCell ref="D13:K18"/>
     <mergeCell ref="A12:C14"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A5:K8"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I3:K3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
